--- a/data/export/2026-10-08-浦东35路.xlsx
+++ b/data/export/2026-10-08-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1381,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1492,1228 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>06:56</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>06:56</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:26</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:26</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-08-浦东35路.xlsx
+++ b/data/export/2026-10-08-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC20"/>
+  <dimension ref="A1:AC31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,20 +436,20 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,33 +693,37 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -743,32 +751,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -776,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,33 +812,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -854,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -887,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,17 +931,17 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -931,13 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -998,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1037,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1048,7 +1072,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1100,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq30推进至seq34，推进4站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1109,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1117,10 +1141,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>物理seq28（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
       <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq28映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
           <t>06:36</t>
@@ -1159,7 +1195,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1306,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1417,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1478,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1528,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1589,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1639,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1700,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1714,7 +1750,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1811,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1825,7 +1861,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1922,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1936,7 +1972,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2033,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2047,7 +2083,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2144,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2158,7 +2194,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2255,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2269,7 +2305,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2366,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2380,7 +2416,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2477,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2491,7 +2527,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2588,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2602,7 +2638,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2699,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2713,7 +2749,1236 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>3/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>1/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-08-浦东35路.xlsx
+++ b/data/export/2026-10-08-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC31"/>
+  <dimension ref="A1:AC37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -761,24 +761,24 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>153分钟</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -880,24 +880,24 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,17 +946,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq30推进至seq34，推进4站，达到≥2站确认条件</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq30推进至seq59，推进29站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1223,32 +1223,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -1256,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1280,33 +1284,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -1334,32 +1342,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1367,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1391,33 +1403,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>152.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1517,7 +1533,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1589,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1628,7 +1644,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1700,7 +1716,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1811,7 +1827,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1889,12 +1905,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq52，推进14站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1922,7 +1938,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1930,10 +1946,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr"/>
-      <c r="S13" s="2" t="inlineStr"/>
-      <c r="T13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>08:26</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq38（站名待映射） ETA 9分钟参与校验</t>
+        </is>
+      </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -2033,7 +2065,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2111,12 +2143,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq44推进至seq47，推进3站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2144,7 +2176,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2152,10 +2184,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q15" s="2" t="inlineStr"/>
-      <c r="R15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>08:36</t>
+        </is>
+      </c>
       <c r="S15" s="2" t="inlineStr"/>
-      <c r="T15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq24映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
           <t>07:24</t>
@@ -2255,7 +2299,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,7 +2410,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2477,7 +2521,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2588,7 +2632,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2699,7 +2743,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2810,7 +2854,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2921,7 +2965,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3143,7 +3187,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3254,7 +3298,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3365,7 +3409,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3476,7 +3520,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3587,7 +3631,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3698,7 +3742,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3747,7 +3791,7 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3813,7 +3857,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3885,7 +3929,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -3928,7 +3972,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3942,7 +3986,7 @@
       <c r="T31" s="2" t="inlineStr"/>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
@@ -3977,6 +4021,684 @@
       </c>
       <c r="AB31" s="2" t="inlineStr"/>
       <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>2/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>152.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>3/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>5/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr">
         <is>
           <t>—/27</t>
         </is>

--- a/data/export/2026-10-08-浦东35路.xlsx
+++ b/data/export/2026-10-08-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -1461,32 +1461,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>168分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1494,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1518,17 +1522,17 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
@@ -1538,13 +1542,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -1572,32 +1580,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>169分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -1605,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1629,17 +1641,17 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
@@ -1649,13 +1661,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>169.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -1683,32 +1699,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>161分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1716,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1740,33 +1760,37 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>161.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1866,7 +1890,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1910,7 +1934,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq52，推进14站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq58，推进20站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1938,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2065,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2104,7 +2128,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2148,7 +2172,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq44推进至seq47，推进3站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq44推进至seq52，推进8站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2176,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2266,32 +2290,36 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -2299,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2323,33 +2351,37 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2449,7 +2481,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2521,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2632,7 +2664,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2743,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2854,7 +2886,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2965,7 +2997,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3187,7 +3219,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3298,7 +3330,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3409,7 +3441,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3520,7 +3552,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3631,7 +3663,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3742,7 +3774,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3796,7 +3828,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -3857,7 +3889,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3972,7 +4004,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4083,7 +4115,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4198,7 +4230,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4309,7 +4341,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4363,7 +4395,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -4424,7 +4456,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4478,7 +4510,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4571,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4583,13 +4615,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB36" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4686,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4694,13 +4730,580 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>169.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>9/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>161.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>7/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB37" s="2" t="inlineStr"/>
-      <c r="AC37" s="2" t="inlineStr">
+      <c r="AB39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
         <is>
           <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr"/>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr"/>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>3/27</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-08-浦东35路.xlsx
+++ b/data/export/2026-10-08-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC42"/>
+  <dimension ref="A1:AC47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>14/27</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -2409,32 +2409,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2442,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2466,17 +2470,17 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
@@ -2486,13 +2490,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -2520,32 +2528,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2553,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2577,33 +2589,37 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -2631,32 +2647,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -2664,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2688,33 +2708,37 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -2742,32 +2766,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2775,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2799,33 +2827,37 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -2853,32 +2885,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>162分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -2886,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2910,33 +2946,37 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>162.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
@@ -2997,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3219,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3258,7 +3298,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3330,7 +3370,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3441,7 +3481,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3552,7 +3592,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3663,7 +3703,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3774,7 +3814,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3828,7 +3868,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3929,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4004,7 +4044,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4115,7 +4155,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4169,7 +4209,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4270,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4341,7 +4381,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4395,7 +4435,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -4456,7 +4496,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4510,7 +4550,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4611,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4625,7 +4665,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -4686,7 +4726,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4740,7 +4780,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>14/27</t>
         </is>
       </c>
     </row>
@@ -4801,7 +4841,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4855,7 +4895,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -4916,7 +4956,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5027,7 +5067,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5138,7 +5178,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5182,13 +5222,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB41" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -5249,7 +5293,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5303,7 +5347,578 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
+          <t>5/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>9/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
           <t>3/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>2/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>162.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>12/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr"/>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-08-浦东35路.xlsx
+++ b/data/export/2026-10-08-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC47"/>
+  <dimension ref="A1:AC52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>14/27</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1901,7 +1901,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2262,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3087,7 +3087,7 @@
       <c r="AB22" s="2" t="inlineStr"/>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       <c r="AB23" s="2" t="inlineStr"/>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3226,32 +3226,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -3259,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3283,17 +3287,17 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3303,13 +3307,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -3337,32 +3345,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3370,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3394,17 +3406,17 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -3414,13 +3426,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -3448,32 +3464,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3481,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3505,17 +3525,17 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3525,13 +3545,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -3592,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3631,7 +3655,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3642,7 +3666,7 @@
       <c r="AB27" s="2" t="inlineStr"/>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3703,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3742,7 +3766,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3753,7 +3777,7 @@
       <c r="AB28" s="2" t="inlineStr"/>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3781,32 +3805,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3814,7 +3842,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3838,17 +3866,17 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
@@ -3858,17 +3886,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -3896,32 +3924,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3929,7 +3961,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3953,17 +3985,17 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -3973,17 +4005,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -4044,7 +4076,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4083,7 +4115,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4094,7 +4126,7 @@
       <c r="AB31" s="2" t="inlineStr"/>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4122,32 +4154,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4155,7 +4191,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4179,17 +4215,17 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
@@ -4199,17 +4235,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4237,12 +4273,12 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq29推进至seq58，推进29站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -4270,18 +4306,30 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>白桦路明月路</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
           <t>10:11</t>
         </is>
       </c>
-      <c r="P33" s="2" t="inlineStr">
-        <is>
-          <t>SHMAAS</t>
-        </is>
-      </c>
-      <c r="Q33" s="2" t="inlineStr"/>
-      <c r="R33" s="2" t="inlineStr"/>
       <c r="S33" s="2" t="inlineStr"/>
-      <c r="T33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq25映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
           <t>09:24</t>
@@ -4320,7 +4368,7 @@
       <c r="AB33" s="2" t="inlineStr"/>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4348,32 +4396,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4381,7 +4433,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4405,17 +4457,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4425,17 +4477,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4548,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4535,7 +4587,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4550,7 +4602,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4663,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4665,7 +4717,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4778,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4780,7 +4832,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>14/27</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -4841,7 +4893,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4895,7 +4947,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -4956,7 +5008,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5006,7 +5058,7 @@
       <c r="AB39" s="2" t="inlineStr"/>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -5067,7 +5119,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5117,7 +5169,7 @@
       <c r="AB40" s="2" t="inlineStr"/>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5230,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5232,7 +5284,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -5293,7 +5345,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5347,7 +5399,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -5408,7 +5460,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5462,7 +5514,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -5523,7 +5575,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5577,7 +5629,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -5638,7 +5690,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5692,7 +5744,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -5753,7 +5805,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5807,7 +5859,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -5815,22 +5867,22 @@
       <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -5863,12 +5915,12 @@
       <c r="M47" s="2" t="inlineStr"/>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5882,7 +5934,7 @@
       <c r="T47" s="2" t="inlineStr"/>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
@@ -5907,7 +5959,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -5918,7 +5970,570 @@
       <c r="AB47" s="2" t="inlineStr"/>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>9/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr"/>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr"/>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr"/>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>11/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-08-浦东35路.xlsx
+++ b/data/export/2026-10-08-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC52"/>
+  <dimension ref="A1:AC57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1304,17 +1304,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1542,17 +1542,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1661,17 +1661,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1895,13 +1895,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,7 +2021,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2028,7 +2032,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2133,13 +2137,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2251,7 +2259,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2262,7 +2270,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2371,17 +2379,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2490,17 +2498,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2619,7 +2627,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2723,7 +2731,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2738,7 +2746,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2857,7 +2865,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2976,7 +2984,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3076,7 +3084,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3087,7 +3095,7 @@
       <c r="AB22" s="2" t="inlineStr"/>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3206,7 @@
       <c r="AB23" s="2" t="inlineStr"/>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3317,7 +3325,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3444,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -3555,7 +3563,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3666,7 +3674,7 @@
       <c r="AB27" s="2" t="inlineStr"/>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3777,7 +3785,7 @@
       <c r="AB28" s="2" t="inlineStr"/>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3896,7 +3904,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4023,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4126,7 +4134,7 @@
       <c r="AB31" s="2" t="inlineStr"/>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4245,7 +4253,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -4278,7 +4286,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq29推进至seq58，推进29站，达到≥2站确认条件</t>
+          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq29推进至seq62，推进33站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -4306,7 +4314,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4368,7 +4376,7 @@
       <c r="AB33" s="2" t="inlineStr"/>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4406,24 +4414,24 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4433,7 +4441,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4482,12 +4490,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -4515,32 +4523,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -4548,7 +4560,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4572,17 +4584,17 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -4592,17 +4604,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -4630,32 +4642,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -4663,7 +4679,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4687,17 +4703,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4707,17 +4723,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -4745,32 +4761,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -4778,7 +4798,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4802,17 +4822,17 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -4822,17 +4842,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4860,32 +4880,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -4893,7 +4917,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4917,17 +4941,17 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4937,17 +4961,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -4975,32 +4999,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5008,7 +5036,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5032,17 +5060,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5052,13 +5080,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB39" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -5086,32 +5118,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5119,7 +5155,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5143,17 +5179,17 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5163,13 +5199,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB40" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -5197,32 +5237,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5230,7 +5274,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5254,17 +5298,17 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5274,17 +5318,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5312,32 +5356,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -5345,7 +5393,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5369,17 +5417,17 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5389,17 +5437,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -5460,7 +5508,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5514,7 +5562,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -5575,7 +5623,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5614,7 +5662,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5629,7 +5677,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -5690,7 +5738,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5744,7 +5792,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5805,7 +5853,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5859,7 +5907,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -5920,7 +5968,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5970,7 +6018,7 @@
       <c r="AB47" s="2" t="inlineStr"/>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6031,7 +6079,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6085,7 +6133,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6194,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6196,7 +6244,7 @@
       <c r="AB49" s="2" t="inlineStr"/>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6257,7 +6305,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6307,7 +6355,7 @@
       <c r="AB50" s="2" t="inlineStr"/>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6416,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6418,7 +6466,7 @@
       <c r="AB51" s="2" t="inlineStr"/>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6479,7 +6527,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6523,17 +6571,576 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>10/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB52" s="2" t="inlineStr">
-        <is>
-          <t>158.0</t>
-        </is>
-      </c>
-      <c r="AC52" s="2" t="inlineStr">
-        <is>
-          <t>11/28</t>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr"/>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr"/>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr"/>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr"/>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>9/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-08-浦东35路.xlsx
+++ b/data/export/2026-10-08-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC57"/>
+  <dimension ref="A1:AC62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2617,17 +2617,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2855,17 +2855,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,22 +2969,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3315,17 +3315,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3663,18 +3663,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB27" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3904,7 +3908,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4088,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4253,7 +4257,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4495,7 +4499,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4560,7 +4564,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4614,7 +4618,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4683,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4718,7 +4722,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4733,7 +4737,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4856,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4971,7 +4975,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -5274,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5313,7 +5317,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5328,7 +5332,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -5366,24 +5370,24 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5393,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5442,12 +5446,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5475,32 +5479,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5508,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5532,17 +5540,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5552,17 +5560,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -5590,32 +5598,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -5623,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5647,17 +5659,17 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5667,12 +5679,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5705,32 +5717,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5738,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5762,17 +5778,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5782,17 +5798,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -5820,32 +5836,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -5853,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5877,37 +5897,37 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -5935,32 +5955,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>10:31</t>
@@ -5968,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5992,33 +6016,37 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB47" s="2" t="inlineStr"/>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -6046,32 +6074,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -6079,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6103,17 +6135,17 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -6123,17 +6155,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6161,32 +6193,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6194,7 +6230,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6218,33 +6254,37 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB49" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6305,7 +6345,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6416,7 +6456,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6527,7 +6567,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6581,7 +6621,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6682,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6753,7 +6793,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6864,7 +6904,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6975,7 +7015,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7086,7 +7126,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7130,17 +7170,592 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>134.5</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>9/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>143.5</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>15/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A72305D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB57" s="2" t="inlineStr">
-        <is>
-          <t>142.0</t>
-        </is>
-      </c>
-      <c r="AC57" s="2" t="inlineStr">
-        <is>
-          <t>9/29</t>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>4/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>18/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>7/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>21/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-08-浦东35路.xlsx
+++ b/data/export/2026-10-08-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC62"/>
+  <dimension ref="A1:AC68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,14 +827,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>140.5</t>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,18 +1061,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1304,17 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,14 +1422,14 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
           <t>143.5</t>
@@ -1433,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1552,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,14 +1779,14 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
           <t>143.0</t>
@@ -1790,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2021,18 +2025,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2389,7 +2397,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2508,7 +2516,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2635,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2746,7 +2754,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2873,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2984,7 +2992,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3320,12 +3328,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3452,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3548,14 +3556,14 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
           <t>146.0</t>
@@ -3563,7 +3571,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3673,12 +3681,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3783,13 +3791,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB28" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3893,14 +3905,14 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
           <t>140.5</t>
@@ -3908,7 +3920,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4027,7 +4039,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4127,18 +4139,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB31" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -4257,7 +4273,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4445,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4484,14 +4500,14 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
           <t>143.5</t>
@@ -4499,7 +4515,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4608,17 +4624,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4737,7 +4753,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4872,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4960,14 +4976,14 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
           <t>143.0</t>
@@ -4975,7 +4991,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5332,7 +5348,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -5451,7 +5467,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -5570,7 +5586,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -5635,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5689,7 +5705,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5824,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5927,7 +5943,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -5992,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6046,7 +6062,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6084,24 +6100,24 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -6111,7 +6127,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6160,12 +6176,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6203,12 +6219,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
@@ -6230,7 +6246,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6279,12 +6295,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6312,32 +6328,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -6345,7 +6365,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6369,17 +6389,17 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6389,13 +6409,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB50" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -6423,32 +6447,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6456,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6480,33 +6508,37 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB51" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -6534,32 +6566,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -6567,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6591,17 +6627,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6611,17 +6647,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6649,12 +6685,12 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq52，推进14站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -6682,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6690,10 +6726,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q53" s="2" t="inlineStr"/>
-      <c r="R53" s="2" t="inlineStr"/>
-      <c r="S53" s="2" t="inlineStr"/>
-      <c r="T53" s="2" t="inlineStr"/>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="T53" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq38（站名待映射） ETA 8分钟参与校验</t>
+        </is>
+      </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
@@ -6760,32 +6812,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -6793,7 +6849,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6817,33 +6873,37 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB54" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -7015,7 +7075,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7126,7 +7186,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7180,7 +7240,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -7241,7 +7301,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7295,7 +7355,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -7356,7 +7416,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7410,7 +7470,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -7471,7 +7531,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7525,7 +7585,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7646,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7635,12 +7695,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -7701,7 +7761,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7755,7 +7815,697 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
+          <t>24/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>140.5</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>16/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>7/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>143.5</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>18/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
           <t>21/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>17/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-08-浦东35路.xlsx
+++ b/data/export/2026-10-08-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC68"/>
+  <dimension ref="A1:AC72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2035,12 +2035,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2267,18 +2267,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -2397,7 +2401,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2466,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2506,17 +2510,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2639,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2744,17 +2748,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2877,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2982,17 +2986,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3097,13 +3101,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -3214,7 +3222,7 @@
       <c r="AB23" s="2" t="inlineStr"/>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3341,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3460,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3571,7 +3579,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3686,7 +3694,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3809,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3920,7 +3928,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -4039,7 +4047,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4154,7 +4162,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -4273,7 +4281,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4385,7 +4393,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4396,7 +4404,7 @@
       <c r="AB33" s="2" t="inlineStr"/>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4515,7 +4523,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4629,12 +4637,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4753,7 +4761,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -4872,7 +4880,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4991,7 +4999,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5095,7 +5103,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5110,7 +5118,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -5229,7 +5237,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5338,17 +5346,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -5467,7 +5475,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -5586,7 +5594,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5695,17 +5703,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -5824,7 +5832,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5933,17 +5941,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6052,17 +6060,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -6181,7 +6189,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -6246,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6300,7 +6308,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6427,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6492,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6538,7 +6546,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -6576,24 +6584,24 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6603,7 +6611,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6652,12 +6660,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -6690,7 +6698,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq52，推进14站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq57，推进19站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -6718,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6784,7 +6792,7 @@
       <c r="AB53" s="2" t="inlineStr"/>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -6822,24 +6830,24 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6849,7 +6857,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6898,12 +6906,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -6931,32 +6939,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6964,7 +6976,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6988,17 +7000,17 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
@@ -7008,13 +7020,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB55" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -7042,32 +7058,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -7075,7 +7095,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7099,33 +7119,37 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB56" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -7153,32 +7177,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7186,7 +7214,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7210,17 +7238,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7230,17 +7258,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -7268,32 +7296,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -7301,7 +7333,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7325,17 +7357,17 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7345,17 +7377,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -7383,32 +7415,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>10:31</t>
@@ -7416,7 +7452,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7440,17 +7476,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7460,17 +7496,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -7498,32 +7534,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -7531,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7555,17 +7595,17 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7575,17 +7615,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -7646,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7700,7 +7740,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -7761,7 +7801,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7815,7 +7855,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7916,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7930,7 +7970,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -7991,7 +8031,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8045,7 +8085,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -8106,7 +8146,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8155,12 +8195,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -8221,7 +8261,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8275,7 +8315,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -8336,7 +8376,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8390,7 +8430,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -8398,22 +8438,22 @@
       <c r="A68" s="2" t="inlineStr"/>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -8446,12 +8486,12 @@
       <c r="M68" s="2" t="inlineStr"/>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8495,17 +8535,469 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr"/>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB68" s="2" t="inlineStr">
+      <c r="AB69" s="2" t="inlineStr">
         <is>
           <t>143.0</t>
         </is>
       </c>
-      <c r="AC68" s="2" t="inlineStr">
-        <is>
-          <t>17/29</t>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>21/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>1/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr"/>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>3/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-08-浦东35路.xlsx
+++ b/data/export/2026-10-08-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC72"/>
+  <dimension ref="A1:AC80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,14 +708,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>127.5</t>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,17 +1066,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>149.7</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,14 +1660,14 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
           <t>150.0</t>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4032,14 +4032,14 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
           <t>127.5</t>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4152,17 +4152,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4746,22 +4746,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>149.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4865,14 +4865,14 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
           <t>150.0</t>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5946,12 +5946,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6298,7 +6298,7 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6427,7 +6427,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6536,17 +6536,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6611,7 +6611,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6650,7 +6650,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -7095,7 +7095,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7333,7 +7333,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -7452,7 +7452,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7544,24 +7544,24 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -7653,32 +7653,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7686,7 +7690,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7710,17 +7714,17 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7730,7 +7734,7 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
@@ -7768,32 +7772,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -7801,7 +7809,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7825,37 +7833,37 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>149.7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -7883,32 +7891,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7916,7 +7928,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7940,17 +7952,17 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
@@ -7960,17 +7972,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7998,32 +8010,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8031,7 +8047,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8055,17 +8071,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8075,17 +8091,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8162,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8261,7 +8277,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8376,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8491,7 +8507,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8602,7 +8618,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8717,7 +8733,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8832,7 +8848,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8890,22 +8906,22 @@
       <c r="A72" s="2" t="inlineStr"/>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -8938,12 +8954,12 @@
       <c r="M72" s="2" t="inlineStr"/>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8987,17 +9003,937 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>127.5</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>6/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB72" s="2" t="inlineStr">
+      <c r="AB73" s="2" t="inlineStr">
         <is>
           <t>126.0</t>
         </is>
       </c>
-      <c r="AC72" s="2" t="inlineStr">
+      <c r="AC73" s="2" t="inlineStr">
         <is>
           <t>3/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>14/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>23/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>17/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>26/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>5/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>149.7</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>25/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>137.7</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>16/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-08-浦东35路.xlsx
+++ b/data/export/2026-10-08-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC80"/>
+  <dimension ref="A1:AC83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>149.7</t>
+          <t>150.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>149.7</t>
+          <t>150.3</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
@@ -7095,7 +7095,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7253,7 +7253,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7782,24 +7782,24 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>149.7</t>
+          <t>150.3</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -7901,24 +7901,24 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8047,7 +8047,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -8129,32 +8129,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -8162,7 +8166,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8186,17 +8190,17 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
@@ -8206,7 +8210,7 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
@@ -8277,7 +8281,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8392,7 +8396,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8507,7 +8511,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8618,7 +8622,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8733,7 +8737,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8959,7 +8963,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9074,7 +9078,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9189,7 +9193,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9304,7 +9308,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9419,7 +9423,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9534,7 +9538,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9588,7 +9592,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -9649,7 +9653,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9764,7 +9768,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9813,12 +9817,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>149.7</t>
+          <t>150.3</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -9826,22 +9830,22 @@
       <c r="A80" s="2" t="inlineStr"/>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>17:20</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -9874,12 +9878,12 @@
       <c r="M80" s="2" t="inlineStr"/>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9918,22 +9922,367 @@
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>135.5</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>15/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA80" s="2" t="inlineStr">
+      <c r="AA81" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB80" s="2" t="inlineStr">
+      <c r="AB81" s="2" t="inlineStr">
         <is>
           <t>137.7</t>
         </is>
       </c>
-      <c r="AC80" s="2" t="inlineStr">
+      <c r="AC81" s="2" t="inlineStr">
         <is>
           <t>16/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>131.7</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>11/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>17/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-08-浦东35路.xlsx
+++ b/data/export/2026-10-08-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC83"/>
+  <dimension ref="A1:AC87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1784,17 +1784,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2272,17 +2272,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3569,17 +3569,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3923,12 +3923,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4508,22 +4508,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4989,17 +4989,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5817,7 +5817,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6055,7 +6055,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7139,17 +7139,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -7452,7 +7452,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -7809,7 +7809,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -8020,24 +8020,24 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -8047,7 +8047,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -8151,12 +8151,12 @@
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8205,7 +8205,7 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -8248,32 +8248,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8281,7 +8285,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8305,37 +8309,37 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -8363,32 +8367,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8396,7 +8404,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8420,17 +8428,17 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
@@ -8440,17 +8448,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -8478,12 +8486,12 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq44，推进16站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -8511,7 +8519,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8519,10 +8527,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q68" s="2" t="inlineStr"/>
-      <c r="R68" s="2" t="inlineStr"/>
-      <c r="S68" s="2" t="inlineStr"/>
-      <c r="T68" s="2" t="inlineStr"/>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>物理seq27（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="S68" s="2" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="T68" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq27映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U68" s="2" t="inlineStr">
         <is>
           <t>15:35</t>
@@ -8589,32 +8613,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -8622,7 +8650,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8646,17 +8674,17 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
@@ -8666,17 +8694,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -8704,32 +8732,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -8737,7 +8769,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8761,17 +8793,17 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
@@ -8781,17 +8813,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -8963,7 +8995,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9078,7 +9110,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9193,7 +9225,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9308,7 +9340,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9362,7 +9394,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -9423,7 +9455,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9477,7 +9509,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -9538,7 +9570,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9653,7 +9685,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9768,7 +9800,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9883,7 +9915,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9998,7 +10030,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10052,7 +10084,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -10113,7 +10145,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10228,7 +10260,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10277,12 +10309,472 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A72305D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>8/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>140.7</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>23/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>1/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>131.5</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>10/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-08-浦东35路.xlsx
+++ b/data/export/2026-10-08-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC87"/>
+  <dimension ref="A1:AC93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2145,17 +2145,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3564,22 +3564,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4032,22 +4032,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4271,17 +4271,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4984,22 +4984,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5108,17 +5108,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -5237,7 +5237,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5341,7 +5341,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6427,7 +6427,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -6611,7 +6611,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7144,12 +7144,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7268,7 +7268,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -7809,7 +7809,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7982,7 +7982,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -8047,7 +8047,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8285,7 +8285,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8339,7 +8339,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -8377,24 +8377,24 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8404,7 +8404,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8443,22 +8443,22 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8491,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq44，推进16站，达到≥2站确认条件</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq64，推进36站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -8519,7 +8519,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8623,24 +8623,24 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8650,7 +8650,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8689,22 +8689,22 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA69" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -8742,24 +8742,24 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8818,12 +8818,12 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -8962,32 +8962,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8995,7 +8999,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9019,37 +9023,37 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -9077,32 +9081,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -9110,7 +9118,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9134,17 +9142,17 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
@@ -9154,17 +9162,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -9192,32 +9200,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9225,7 +9237,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9249,17 +9261,17 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
@@ -9269,17 +9281,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -9340,7 +9352,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9455,7 +9467,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9494,7 +9506,7 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9570,7 +9582,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9685,7 +9697,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9739,7 +9751,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -9800,7 +9812,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9915,7 +9927,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9969,7 +9981,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -10030,7 +10042,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10084,7 +10096,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -10145,7 +10157,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10199,7 +10211,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -10260,7 +10272,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10375,7 +10387,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10429,7 +10441,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -10490,7 +10502,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10544,7 +10556,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -10605,7 +10617,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10720,7 +10732,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10774,7 +10786,697 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>8/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>6/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>20/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>17/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>141.3</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>23/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>18/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>12/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-08-浦东35路.xlsx
+++ b/data/export/2026-10-08-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC93"/>
+  <dimension ref="A1:AC99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>150.3</t>
+          <t>153.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,17 +1660,17 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>148.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3794,22 +3794,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4266,22 +4266,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4632,17 +4632,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4751,12 +4751,12 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>150.3</t>
+          <t>153.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4865,17 +4865,17 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>148.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6179,12 +6179,12 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6412,22 +6412,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -6611,7 +6611,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6655,17 +6655,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7134,7 +7134,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7268,7 +7268,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -7452,7 +7452,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -7625,7 +7625,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -7809,7 +7809,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7853,12 +7853,12 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>150.3</t>
+          <t>153.8</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7982,7 +7982,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -8047,7 +8047,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8101,7 +8101,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -8166,7 +8166,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8285,7 +8285,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8404,7 +8404,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -8650,7 +8650,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8808,7 +8808,7 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
@@ -8823,7 +8823,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -8999,7 +8999,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9053,7 +9053,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9157,7 +9157,7 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
@@ -9172,7 +9172,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -9210,24 +9210,24 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>145分钟</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9276,22 +9276,22 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA74" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -9352,7 +9352,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9391,7 +9391,7 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9434,32 +9434,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -9467,7 +9471,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9491,17 +9495,17 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
@@ -9511,12 +9515,12 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9549,32 +9553,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -9582,7 +9590,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9606,32 +9614,32 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA77" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>148.7</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9664,32 +9672,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -9697,7 +9709,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9721,37 +9733,37 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -9779,32 +9791,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>164分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -9812,7 +9828,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9836,17 +9852,17 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
@@ -9856,12 +9872,12 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>150.3</t>
+          <t>153.8</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
@@ -9894,32 +9910,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -9927,7 +9947,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9951,17 +9971,17 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
@@ -9971,12 +9991,12 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -10009,32 +10029,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -10042,7 +10066,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10066,17 +10090,17 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -10086,17 +10110,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -10157,7 +10181,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10211,7 +10235,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -10272,7 +10296,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10326,7 +10350,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -10387,7 +10411,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10441,7 +10465,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -10502,7 +10526,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10617,7 +10641,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10732,7 +10756,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10786,7 +10810,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -10847,7 +10871,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10901,7 +10925,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -10962,7 +10986,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11016,7 +11040,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -11077,7 +11101,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11131,7 +11155,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -11192,7 +11216,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11307,7 +11331,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11351,12 +11375,12 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
@@ -11422,7 +11446,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11476,7 +11500,697 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>11/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>127.5</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>3/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>134.5</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>13/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>138.7</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>16/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>24/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>148.7</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>25/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-08-浦东35路.xlsx
+++ b/data/export/2026-10-08-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC99"/>
+  <dimension ref="A1:AC102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>153.8</t>
+          <t>154.2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2386,22 +2386,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2748,17 +2748,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>131.7</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2862,22 +2862,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2981,14 +2981,14 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
           <t>140.0</t>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>153.8</t>
+          <t>154.2</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5460,22 +5460,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5703,17 +5703,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>131.7</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5817,22 +5817,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5936,14 +5936,14 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
           <t>140.0</t>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6060,17 +6060,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6427,7 +6427,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6611,7 +6611,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7020,12 +7020,12 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7095,7 +7095,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7258,17 +7258,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>131.7</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -7452,7 +7452,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7496,17 +7496,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7610,14 +7610,14 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
           <t>140.0</t>
@@ -7625,7 +7625,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7809,7 +7809,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>153.8</t>
+          <t>154.2</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -8047,7 +8047,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8091,17 +8091,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -8285,7 +8285,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8329,12 +8329,12 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8404,7 +8404,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -8650,7 +8650,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8884,7 +8884,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9053,7 +9053,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9172,7 +9172,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -9237,7 +9237,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9291,7 +9291,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -9352,7 +9352,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9525,7 +9525,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -9801,24 +9801,24 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>19:46</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>164分钟</t>
+          <t>166分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -9828,7 +9828,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>153.8</t>
+          <t>154.2</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
@@ -9920,19 +9920,19 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>19:46</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
@@ -9947,7 +9947,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9986,22 +9986,22 @@
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA80" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -10066,7 +10066,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -10148,32 +10148,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10181,7 +10185,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10205,17 +10209,17 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
@@ -10225,17 +10229,17 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>131.7</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -10263,32 +10267,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10296,7 +10304,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10320,17 +10328,17 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
@@ -10340,17 +10348,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -10378,32 +10386,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>10:31</t>
@@ -10411,7 +10423,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10435,17 +10447,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10455,17 +10467,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -10493,32 +10505,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10526,7 +10542,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10550,17 +10566,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10570,12 +10586,12 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
@@ -10723,32 +10739,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -10756,7 +10776,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10780,37 +10800,37 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA87" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -10838,32 +10858,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10871,7 +10895,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10895,17 +10919,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10915,12 +10939,12 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
@@ -10986,7 +11010,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11040,7 +11064,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -11101,7 +11125,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11155,7 +11179,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -11216,7 +11240,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11331,7 +11355,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11385,7 +11409,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11470,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11500,7 +11524,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -11561,7 +11585,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11615,7 +11639,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -11676,7 +11700,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11791,7 +11815,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11845,7 +11869,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -11906,7 +11930,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11960,7 +11984,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -12021,7 +12045,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12083,22 +12107,22 @@
       <c r="A99" s="2" t="inlineStr"/>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>20:05</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -12131,12 +12155,12 @@
       <c r="M99" s="2" t="inlineStr"/>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12150,47 +12174,392 @@
       <c r="T99" s="2" t="inlineStr"/>
       <c r="U99" s="2" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>17/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
           <t>20:05</t>
         </is>
       </c>
-      <c r="V99" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W99" s="2" t="inlineStr">
+      <c r="W100" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X99" s="2" t="inlineStr">
+      <c r="X100" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y99" s="2" t="inlineStr">
+      <c r="Y100" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z99" s="2" t="inlineStr">
+      <c r="Z100" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA99" s="2" t="inlineStr">
+      <c r="AA100" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB99" s="2" t="inlineStr">
+      <c r="AB100" s="2" t="inlineStr">
         <is>
           <t>148.7</t>
         </is>
       </c>
-      <c r="AC99" s="2" t="inlineStr">
+      <c r="AC100" s="2" t="inlineStr">
         <is>
           <t>25/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>16/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>6/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-08-浦东35路.xlsx
+++ b/data/export/2026-10-08-浦东35路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1784,17 +1784,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2145,17 +2145,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2629,17 +2629,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3569,17 +3569,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4037,17 +4037,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -4523,7 +4523,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4989,17 +4989,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5108,17 +5108,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5584,17 +5584,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -5713,7 +5713,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -6070,7 +6070,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6427,7 +6427,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -6665,7 +6665,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7095,7 +7095,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7268,7 +7268,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -8339,7 +8339,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -8404,7 +8404,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8448,17 +8448,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -8650,7 +8650,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8694,17 +8694,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -8769,7 +8769,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8884,7 +8884,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9043,17 +9043,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9162,17 +9162,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -9237,7 +9237,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9291,7 +9291,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -9352,7 +9352,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9396,17 +9396,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -9471,7 +9471,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9525,7 +9525,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -9947,7 +9947,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10001,7 +10001,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -10239,7 +10239,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -10477,7 +10477,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -10776,7 +10776,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10880,12 +10880,12 @@
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -10895,7 +10895,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10977,32 +10977,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -11010,7 +11014,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11034,17 +11038,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -11054,12 +11058,12 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
@@ -11092,32 +11096,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11125,7 +11133,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11149,17 +11157,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11169,17 +11177,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -11207,32 +11215,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -11240,7 +11252,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11264,17 +11276,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11284,17 +11296,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -11322,12 +11334,12 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq30推进至seq60，推进30站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -11355,7 +11367,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11363,10 +11375,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q92" s="2" t="inlineStr"/>
-      <c r="R92" s="2" t="inlineStr"/>
-      <c r="S92" s="2" t="inlineStr"/>
-      <c r="T92" s="2" t="inlineStr"/>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>物理seq31（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr">
+        <is>
+          <t>20:04</t>
+        </is>
+      </c>
+      <c r="S92" s="2" t="inlineStr">
+        <is>
+          <t>20:12</t>
+        </is>
+      </c>
+      <c r="T92" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq31映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq30（站名待映射） ETA 4分钟参与校验</t>
+        </is>
+      </c>
       <c r="U92" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -11409,7 +11437,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -11437,32 +11465,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:18</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11470,7 +11502,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11494,17 +11526,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11514,17 +11546,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -11552,32 +11584,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:26</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -11585,7 +11621,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11609,17 +11645,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11629,17 +11665,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -11700,7 +11736,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11782,12 +11818,12 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq56，推进28站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -11815,7 +11851,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11823,10 +11859,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q96" s="2" t="inlineStr"/>
-      <c r="R96" s="2" t="inlineStr"/>
-      <c r="S96" s="2" t="inlineStr"/>
-      <c r="T96" s="2" t="inlineStr"/>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>物理seq27（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr">
+        <is>
+          <t>20:14</t>
+        </is>
+      </c>
+      <c r="S96" s="2" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="T96" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq27映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U96" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -11869,7 +11921,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -11930,7 +11982,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11984,7 +12036,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -12012,32 +12064,36 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -12045,7 +12101,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12069,17 +12125,17 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
@@ -12089,17 +12145,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -12160,7 +12216,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12214,7 +12270,7 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -12275,7 +12331,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12390,7 +12446,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12444,7 +12500,7 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -12505,7 +12561,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
